--- a/Stats Sheet/Round Gaps/Alphabetrum Reboot.xlsx
+++ b/Stats Sheet/Round Gaps/Alphabetrum Reboot.xlsx
@@ -28,6 +28,9 @@
     <x:t>4</x:t>
   </x:si>
   <x:si>
+    <x:t>5</x:t>
+  </x:si>
+  <x:si>
     <x:t>_carn</x:t>
   </x:si>
   <x:si>
@@ -88,6 +91,9 @@
     <x:t>dahii</x:t>
   </x:si>
   <x:si>
+    <x:t>282</x:t>
+  </x:si>
+  <x:si>
     <x:t>DevoyTTV</x:t>
   </x:si>
   <x:si>
@@ -118,6 +124,9 @@
     <x:t>grantfaker</x:t>
   </x:si>
   <x:si>
+    <x:t>205</x:t>
+  </x:si>
+  <x:si>
     <x:t>Karliffu</x:t>
   </x:si>
   <x:si>
@@ -272,6 +281,60 @@
   </x:si>
   <x:si>
     <x:t>vynil</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Br8dy_</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ChrisCD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CodeJoshua</x:t>
+  </x:si>
+  <x:si>
+    <x:t>flameh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gleoss</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItzBeeZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JampoJohn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kaimaxon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lighte</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nsket</x:t>
+  </x:si>
+  <x:si>
+    <x:t>omchris</x:t>
+  </x:si>
+  <x:si>
+    <x:t>onstep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OOGAABOOGA3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>painterwanabe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pgy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sgouche</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ShootingGoats</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zCent</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -630,10 +693,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:H81"/>
+  <x:dimension ref="A1:I99"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:8" s="1" customFormat="1">
+    <x:row r="1" spans="1:9" s="1" customFormat="1">
       <x:c r="E1" s="1">
         <x:v>45837</x:v>
       </x:c>
@@ -646,8 +709,11 @@
       <x:c r="H1" s="1">
         <x:v>46020</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:8">
+      <x:c r="I1" s="1">
+        <x:v>46119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:9">
       <x:c r="F2" s="0">
         <x:v>41</x:v>
       </x:c>
@@ -657,8 +723,11 @@
       <x:c r="H2" s="0">
         <x:v>106</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" spans="1:8">
+      <x:c r="I2" s="0">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:9">
       <x:c r="E3" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -671,105 +740,120 @@
       <x:c r="H3" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" spans="1:8">
+      <x:c r="I3" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:9">
       <x:c r="A4" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:9">
       <x:c r="A5" s="0">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D5" s="0">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D5" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:9">
       <x:c r="A6" s="0">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:9">
       <x:c r="A7" s="0">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:9">
       <x:c r="A8" s="0">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
         <x:v>0</x:v>
@@ -778,41 +862,44 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:9">
       <x:c r="A9" s="0">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:8">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:9">
       <x:c r="A10" s="0">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>0</x:v>
@@ -821,21 +908,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:9">
       <x:c r="A11" s="0">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
         <x:v>0</x:v>
@@ -844,93 +931,102 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:8">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:9">
       <x:c r="A12" s="0">
         <x:v>9</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D12" s="0">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D12" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H12" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:8">
+      <x:c r="I12" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:9">
       <x:c r="A13" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:8">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I13" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:9">
       <x:c r="A14" s="0">
         <x:v>11</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I14" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:9">
       <x:c r="A15" s="0">
         <x:v>12</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
         <x:v>0</x:v>
@@ -939,15 +1035,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:9">
       <x:c r="A16" s="0">
         <x:v>13</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
         <x:v>0</x:v>
@@ -956,21 +1052,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:9">
       <x:c r="A17" s="0">
         <x:v>14</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
         <x:v>0</x:v>
@@ -979,153 +1075,171 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:9">
       <x:c r="A18" s="0">
         <x:v>15</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I18" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:9">
       <x:c r="A19" s="0">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I19" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:9">
       <x:c r="A20" s="0">
         <x:v>17</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I20" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:9">
       <x:c r="A21" s="0">
         <x:v>18</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:8">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I21" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:9">
       <x:c r="A22" s="0">
         <x:v>19</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:8">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I22" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:9">
       <x:c r="A23" s="0">
         <x:v>20</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:8">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I23" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:9">
       <x:c r="A24" s="0">
         <x:v>21</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
         <x:v>0</x:v>
@@ -1134,18 +1248,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:9">
       <x:c r="A25" s="0">
         <x:v>22</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
         <x:v>0</x:v>
@@ -1154,35 +1268,38 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:9">
       <x:c r="A26" s="0">
         <x:v>23</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I26" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:9">
       <x:c r="A27" s="0">
         <x:v>24</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
         <x:v>0</x:v>
@@ -1191,18 +1308,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:9">
       <x:c r="A28" s="0">
         <x:v>25</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
         <x:v>0</x:v>
@@ -1211,90 +1328,99 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H28" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:8">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:9">
       <x:c r="A29" s="0">
         <x:v>26</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I29" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:9">
       <x:c r="A30" s="0">
         <x:v>27</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H30" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I30" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:9">
       <x:c r="A31" s="0">
         <x:v>28</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H31" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I31" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:9">
       <x:c r="A32" s="0">
         <x:v>29</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
         <x:v>0</x:v>
@@ -1303,32 +1429,35 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:9">
       <x:c r="A33" s="0">
         <x:v>30</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I33" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:9">
       <x:c r="A34" s="0">
         <x:v>31</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
         <x:v>0</x:v>
@@ -1337,15 +1466,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:9">
       <x:c r="A35" s="0">
         <x:v>32</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
         <x:v>0</x:v>
@@ -1354,21 +1483,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H35" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:8">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:9">
       <x:c r="A36" s="0">
         <x:v>33</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
         <x:v>0</x:v>
@@ -1377,18 +1506,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:9">
       <x:c r="A37" s="0">
         <x:v>34</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
         <x:v>0</x:v>
@@ -1397,44 +1526,47 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:9">
       <x:c r="A38" s="0">
         <x:v>35</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G38" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H38" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I38" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:9">
       <x:c r="A39" s="0">
         <x:v>36</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
         <x:v>0</x:v>
@@ -1443,15 +1575,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:9">
       <x:c r="A40" s="0">
         <x:v>37</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
         <x:v>0</x:v>
@@ -1460,38 +1592,41 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H40" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:8">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:9">
       <x:c r="A41" s="0">
         <x:v>38</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H41" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:8">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I41" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:9">
       <x:c r="A42" s="0">
         <x:v>39</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
         <x:v>1</x:v>
@@ -1500,84 +1635,93 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G42" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:9">
       <x:c r="A43" s="0">
         <x:v>40</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F43" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G43" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H43" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I43" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:9">
       <x:c r="A44" s="0">
         <x:v>41</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F44" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G44" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H44" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I44" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:9">
       <x:c r="A45" s="0">
         <x:v>42</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F45" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G45" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I45" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:9">
       <x:c r="A46" s="0">
         <x:v>43</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
         <x:v>1</x:v>
@@ -1586,35 +1730,38 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F46" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:9">
       <x:c r="A47" s="0">
         <x:v>44</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F47" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H47" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:8">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I47" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:9">
       <x:c r="A48" s="0">
         <x:v>45</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
         <x:v>1</x:v>
@@ -1623,38 +1770,41 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F48" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:9">
       <x:c r="A49" s="0">
         <x:v>46</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F49" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G49" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H49" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I49" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:9">
       <x:c r="A50" s="0">
         <x:v>47</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
         <x:v>1</x:v>
@@ -1663,21 +1813,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="F50" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G50" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H50" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:9">
       <x:c r="A51" s="0">
         <x:v>48</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
         <x:v>1</x:v>
@@ -1686,35 +1836,38 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F51" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:9">
       <x:c r="A52" s="0">
         <x:v>49</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G52" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H52" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I52" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:9">
       <x:c r="A53" s="0">
         <x:v>50</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
         <x:v>2</x:v>
@@ -1723,15 +1876,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G53" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:9">
       <x:c r="A54" s="0">
         <x:v>51</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
         <x:v>2</x:v>
@@ -1740,72 +1893,81 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G54" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:9">
       <x:c r="A55" s="0">
         <x:v>52</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D55" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G55" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I55" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:9">
       <x:c r="A56" s="0">
         <x:v>53</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D56" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G56" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H56" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I56" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:9">
       <x:c r="A57" s="0">
         <x:v>54</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D57" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G57" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H57" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I57" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:9">
       <x:c r="A58" s="0">
         <x:v>55</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
         <x:v>2</x:v>
@@ -1814,15 +1976,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G58" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:9">
       <x:c r="A59" s="0">
         <x:v>56</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
         <x:v>2</x:v>
@@ -1831,35 +1993,38 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G59" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:9">
       <x:c r="A60" s="0">
         <x:v>57</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D60" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G60" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H60" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I60" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:9">
       <x:c r="A61" s="0">
         <x:v>58</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
         <x:v>2</x:v>
@@ -1868,18 +2033,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="G61" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H61" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:9">
       <x:c r="A62" s="0">
         <x:v>59</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
         <x:v>2</x:v>
@@ -1888,109 +2053,124 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G62" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:9">
       <x:c r="A63" s="0">
         <x:v>60</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D63" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G63" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I63" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:9">
       <x:c r="A64" s="0">
         <x:v>61</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D64" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G64" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H64" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I64" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:9">
       <x:c r="A65" s="0">
         <x:v>62</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D65" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G65" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H65" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I65" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:9">
       <x:c r="A66" s="0">
         <x:v>63</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D66" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G66" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H66" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I66" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:9">
       <x:c r="A67" s="0">
         <x:v>64</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D67" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G67" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="68" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I67" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:9">
       <x:c r="A68" s="0">
         <x:v>65</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
         <x:v>2</x:v>
@@ -1999,35 +2179,38 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G68" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:9">
       <x:c r="A69" s="0">
         <x:v>66</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D69" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G69" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H69" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="70" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I69" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:9">
       <x:c r="A70" s="0">
         <x:v>67</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
         <x:v>2</x:v>
@@ -2036,18 +2219,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="G70" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H70" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="71" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:9">
       <x:c r="A71" s="0">
         <x:v>68</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
         <x:v>2</x:v>
@@ -2056,18 +2239,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="G71" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H71" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="72" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:9">
       <x:c r="A72" s="0">
         <x:v>69</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
         <x:v>2</x:v>
@@ -2076,15 +2259,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G72" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:9">
       <x:c r="A73" s="0">
         <x:v>70</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
         <x:v>2</x:v>
@@ -2093,18 +2276,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="G73" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H73" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="74" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:9">
       <x:c r="A74" s="0">
         <x:v>71</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
         <x:v>2</x:v>
@@ -2113,15 +2296,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G74" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="75" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:9">
       <x:c r="A75" s="0">
         <x:v>72</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
         <x:v>2</x:v>
@@ -2130,15 +2313,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G75" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="76" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:9">
       <x:c r="A76" s="0">
         <x:v>73</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
         <x:v>2</x:v>
@@ -2147,35 +2330,38 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="G76" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H76" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="77" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:9">
       <x:c r="A77" s="0">
         <x:v>74</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D77" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H77" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="78" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I77" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:9">
       <x:c r="A78" s="0">
         <x:v>75</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
         <x:v>3</x:v>
@@ -2184,15 +2370,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H78" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="79" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:9">
       <x:c r="A79" s="0">
         <x:v>76</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
         <x:v>3</x:v>
@@ -2201,15 +2387,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H79" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="80" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:9">
       <x:c r="A80" s="0">
         <x:v>77</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
         <x:v>3</x:v>
@@ -2218,24 +2404,333 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H80" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="81" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:9">
       <x:c r="A81" s="0">
         <x:v>78</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D81" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H81" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I81" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:9">
+      <x:c r="A82" s="0">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B82" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C82" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D82" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I82" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:9">
+      <x:c r="A83" s="0">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B83" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C83" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D83" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I83" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:9">
+      <x:c r="A84" s="0">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B84" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C84" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D84" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I84" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:9">
+      <x:c r="A85" s="0">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B85" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C85" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D85" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I85" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" spans="1:9">
+      <x:c r="A86" s="0">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B86" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C86" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D86" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I86" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" spans="1:9">
+      <x:c r="A87" s="0">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B87" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C87" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D87" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I87" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" spans="1:9">
+      <x:c r="A88" s="0">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B88" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C88" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D88" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I88" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" spans="1:9">
+      <x:c r="A89" s="0">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B89" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C89" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D89" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I89" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" spans="1:9">
+      <x:c r="A90" s="0">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B90" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C90" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D90" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I90" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:9">
+      <x:c r="A91" s="0">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B91" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C91" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D91" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I91" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:9">
+      <x:c r="A92" s="0">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B92" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C92" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D92" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I92" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:9">
+      <x:c r="A93" s="0">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B93" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C93" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D93" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I93" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:9">
+      <x:c r="A94" s="0">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B94" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C94" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D94" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I94" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:9">
+      <x:c r="A95" s="0">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B95" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C95" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D95" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I95" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:9">
+      <x:c r="A96" s="0">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B96" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C96" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D96" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I96" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:9">
+      <x:c r="A97" s="0">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B97" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C97" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D97" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I97" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:9">
+      <x:c r="A98" s="0">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B98" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C98" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D98" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I98" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:9">
+      <x:c r="A99" s="0">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B99" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="C99" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D99" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I99" s="0" t="s">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
